--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260831.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260831.xlsx
@@ -777,17 +777,17 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>114,693,168</t>
+          <t>194,237,978</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -799,17 +799,17 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>194,237,978</t>
+          <t>114,693,168</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
